--- a/extension/results/poisson_exact_results.xlsx
+++ b/extension/results/poisson_exact_results.xlsx
@@ -5,10 +5,10 @@
   <workbookPr dateCompatibility="0" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/stevehalley/Code/Github/QuantumHypergraphPartitioning/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/stevehalley/Code/Github/QuantumHypergraphPartitioning/extension/results/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5DD95F2C-44F0-5B4C-98A1-D22A07237B77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{522E3D13-87D8-0E46-8F12-2ED640567977}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5180" yWindow="1880" windowWidth="28040" windowHeight="17180" xr2:uid="{74AD1E4D-F565-204F-B221-CA17FA357052}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" count="131" uniqueCount="75">
+<sst xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" count="132" uniqueCount="76">
   <si>
     <t>dataset</t>
   </si>
@@ -261,6 +261,9 @@
   </si>
   <si>
     <t>1110111110100101</t>
+  </si>
+  <si>
+    <t>mtkahypar</t>
   </si>
 </sst>
 </file>
@@ -1133,15 +1136,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" xmlns:r="http://purl.oclc.org/ooxml/officeDocument/relationships" xmlns:v="urn:schemas-microsoft-com:vml" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C8E7D524-8200-7840-AD92-882A24A88ACB}">
-  <dimension ref="A1:J41"/>
+  <dimension ref="A1:I41"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="14.83203125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="17.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="20" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="19.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1166,8 +1170,11 @@
       <c r="H1" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="I1" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -1195,12 +1202,8 @@
       <c r="I2">
         <v>6</v>
       </c>
-      <c r="J2">
-        <f>G2-I2</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>8</v>
       </c>
@@ -1228,12 +1231,8 @@
       <c r="I3">
         <v>6</v>
       </c>
-      <c r="J3">
-        <f t="shared" ref="J3:J41" si="0">G3-I3</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>8</v>
       </c>
@@ -1261,12 +1260,8 @@
       <c r="I4">
         <v>8</v>
       </c>
-      <c r="J4">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>8</v>
       </c>
@@ -1294,12 +1289,8 @@
       <c r="I5">
         <v>10</v>
       </c>
-      <c r="J5">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>8</v>
       </c>
@@ -1327,12 +1318,8 @@
       <c r="I6">
         <v>7</v>
       </c>
-      <c r="J6">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -1360,12 +1347,8 @@
       <c r="I7">
         <v>10</v>
       </c>
-      <c r="J7">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>8</v>
       </c>
@@ -1393,12 +1376,8 @@
       <c r="I8">
         <v>8</v>
       </c>
-      <c r="J8">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>8</v>
       </c>
@@ -1426,12 +1405,8 @@
       <c r="I9">
         <v>7</v>
       </c>
-      <c r="J9">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>8</v>
       </c>
@@ -1459,12 +1434,8 @@
       <c r="I10">
         <v>9</v>
       </c>
-      <c r="J10">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>8</v>
       </c>
@@ -1492,12 +1463,8 @@
       <c r="I11">
         <v>7</v>
       </c>
-      <c r="J11">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>8</v>
       </c>
@@ -1525,12 +1492,8 @@
       <c r="I12">
         <v>7</v>
       </c>
-      <c r="J12">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>8</v>
       </c>
@@ -1558,12 +1521,8 @@
       <c r="I13">
         <v>7</v>
       </c>
-      <c r="J13">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>8</v>
       </c>
@@ -1591,12 +1550,8 @@
       <c r="I14">
         <v>10</v>
       </c>
-      <c r="J14">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>8</v>
       </c>
@@ -1624,12 +1579,8 @@
       <c r="I15">
         <v>7</v>
       </c>
-      <c r="J15">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>8</v>
       </c>
@@ -1657,12 +1608,8 @@
       <c r="I16">
         <v>8</v>
       </c>
-      <c r="J16">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.2">
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>8</v>
       </c>
@@ -1690,12 +1637,8 @@
       <c r="I17">
         <v>8</v>
       </c>
-      <c r="J17">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.2">
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>8</v>
       </c>
@@ -1723,12 +1666,8 @@
       <c r="I18">
         <v>5</v>
       </c>
-      <c r="J18">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.2">
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>8</v>
       </c>
@@ -1756,12 +1695,8 @@
       <c r="I19">
         <v>7</v>
       </c>
-      <c r="J19">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.2">
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>8</v>
       </c>
@@ -1789,12 +1724,8 @@
       <c r="I20">
         <v>7</v>
       </c>
-      <c r="J20">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.2">
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>8</v>
       </c>
@@ -1822,12 +1753,8 @@
       <c r="I21">
         <v>6</v>
       </c>
-      <c r="J21">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.2">
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>47</v>
       </c>
@@ -1852,15 +1779,8 @@
       <c r="H22" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="I22">
-        <v>10</v>
-      </c>
-      <c r="J22">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.2">
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>47</v>
       </c>
@@ -1885,15 +1805,8 @@
       <c r="H23" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="I23">
-        <v>10</v>
-      </c>
-      <c r="J23">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.2">
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>47</v>
       </c>
@@ -1918,15 +1831,8 @@
       <c r="H24" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="I24">
-        <v>10</v>
-      </c>
-      <c r="J24">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.2">
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>47</v>
       </c>
@@ -1951,15 +1857,8 @@
       <c r="H25" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="I25">
-        <v>10</v>
-      </c>
-      <c r="J25">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.2">
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>47</v>
       </c>
@@ -1984,15 +1883,8 @@
       <c r="H26" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="I26">
-        <v>9</v>
-      </c>
-      <c r="J26">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.2">
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>47</v>
       </c>
@@ -2017,15 +1909,8 @@
       <c r="H27" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="I27">
-        <v>11</v>
-      </c>
-      <c r="J27">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.2">
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>47</v>
       </c>
@@ -2050,15 +1935,8 @@
       <c r="H28" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="I28">
-        <v>12</v>
-      </c>
-      <c r="J28">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.2">
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>47</v>
       </c>
@@ -2083,15 +1961,8 @@
       <c r="H29" s="2">
         <v>101111010110011</v>
       </c>
-      <c r="I29">
-        <v>9</v>
-      </c>
-      <c r="J29">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.2">
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>47</v>
       </c>
@@ -2116,15 +1987,8 @@
       <c r="H30" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="I30">
-        <v>10</v>
-      </c>
-      <c r="J30">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.2">
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>47</v>
       </c>
@@ -2149,15 +2013,8 @@
       <c r="H31" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="I31">
-        <v>10</v>
-      </c>
-      <c r="J31">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.2">
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>61</v>
       </c>
@@ -2182,15 +2039,8 @@
       <c r="H32" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="I32">
-        <v>12</v>
-      </c>
-      <c r="J32">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.2">
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>61</v>
       </c>
@@ -2215,15 +2065,8 @@
       <c r="H33" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="I33">
-        <v>13</v>
-      </c>
-      <c r="J33">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.2">
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>61</v>
       </c>
@@ -2248,15 +2091,8 @@
       <c r="H34" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="I34">
-        <v>13</v>
-      </c>
-      <c r="J34">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.2">
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>61</v>
       </c>
@@ -2281,15 +2117,8 @@
       <c r="H35" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="I35">
-        <v>13</v>
-      </c>
-      <c r="J35">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.2">
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>61</v>
       </c>
@@ -2314,15 +2143,8 @@
       <c r="H36" s="2">
         <v>111001111110110</v>
       </c>
-      <c r="I36">
-        <v>11</v>
-      </c>
-      <c r="J36">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.2">
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>61</v>
       </c>
@@ -2347,15 +2169,8 @@
       <c r="H37" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="I37">
-        <v>12</v>
-      </c>
-      <c r="J37">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.2">
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>61</v>
       </c>
@@ -2380,15 +2195,8 @@
       <c r="H38" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="I38">
-        <v>11</v>
-      </c>
-      <c r="J38">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.2">
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>61</v>
       </c>
@@ -2413,15 +2221,8 @@
       <c r="H39" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="I39">
-        <v>13</v>
-      </c>
-      <c r="J39">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.2">
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>61</v>
       </c>
@@ -2446,15 +2247,8 @@
       <c r="H40" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="I40">
-        <v>11</v>
-      </c>
-      <c r="J40">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.2">
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>61</v>
       </c>
@@ -2478,13 +2272,6 @@
       </c>
       <c r="H41" s="1" t="s">
         <v>74</v>
-      </c>
-      <c r="I41">
-        <v>11</v>
-      </c>
-      <c r="J41">
-        <f t="shared" si="0"/>
-        <v>0</v>
       </c>
     </row>
   </sheetData>
